--- a/MYNTRA.xlsx
+++ b/MYNTRA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a78d3890a4253b6d/Desktop/java/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{E4912E58-961C-4DF0-AEB4-B27FD511F8B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3DEA55D-C28C-4B2D-9774-1499B4E7AB00}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="8_{E4912E58-961C-4DF0-AEB4-B27FD511F8B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9485F2C-52FD-450D-A58B-4CFB16F187E9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1B63074A-5729-4224-9B6A-8F80C0CCCF15}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="111">
   <si>
     <t>TC ID</t>
   </si>
@@ -56,12 +56,6 @@
     <t>TC01</t>
   </si>
   <si>
-    <t>Valid Login</t>
-  </si>
-  <si>
-    <t>User should login successfully</t>
-  </si>
-  <si>
     <t>User logged in successfully</t>
   </si>
   <si>
@@ -71,27 +65,15 @@
     <t>TC02</t>
   </si>
   <si>
-    <t>Invalid Login</t>
-  </si>
-  <si>
-    <t>Error message should be displayed</t>
-  </si>
-  <si>
     <t>Fail</t>
   </si>
   <si>
     <t>TC03</t>
   </si>
   <si>
-    <t>Product Availability</t>
-  </si>
-  <si>
     <t>TC04</t>
   </si>
   <si>
-    <t>Out-of-Stock Product</t>
-  </si>
-  <si>
     <t>TC05</t>
   </si>
   <si>
@@ -101,42 +83,21 @@
     <t>TC07</t>
   </si>
   <si>
-    <t>Valid Quantity</t>
-  </si>
-  <si>
-    <t>Quantity should be accepted</t>
-  </si>
-  <si>
-    <t>Quantity accepted</t>
-  </si>
-  <si>
     <t>TC08</t>
   </si>
   <si>
     <t>TC09</t>
   </si>
   <si>
-    <t>Add to Bag</t>
-  </si>
-  <si>
     <t>TC10</t>
   </si>
   <si>
-    <t>Invalid Address</t>
-  </si>
-  <si>
-    <t>Address validation error should appear</t>
-  </si>
-  <si>
     <t>TC11</t>
   </si>
   <si>
     <t>TC12</t>
   </si>
   <si>
-    <t>Place Order</t>
-  </si>
-  <si>
     <t>Order should be placed successfully</t>
   </si>
   <si>
@@ -152,24 +113,12 @@
     <t>Product details displayed</t>
   </si>
   <si>
-    <t>Out-of-stock message should be displayed</t>
-  </si>
-  <si>
-    <t>Product can be added to Bag</t>
-  </si>
-  <si>
-    <t>Valid Size Selection</t>
-  </si>
-  <si>
     <t>Selected size should be accepted</t>
   </si>
   <si>
     <t>Size selected successfully</t>
   </si>
   <si>
-    <t>Invalid Size Selection</t>
-  </si>
-  <si>
     <t>Unavailable size should not be selectable</t>
   </si>
   <si>
@@ -218,27 +167,18 @@
     <t>(Passed ÷ Total) × 100</t>
   </si>
   <si>
-    <t>(8 ÷ 12) × 100 = 66.67%</t>
-  </si>
-  <si>
     <t>Fail Rate</t>
   </si>
   <si>
     <t>(Failed ÷ Total) × 100</t>
   </si>
   <si>
-    <t>(4 ÷ 12) × 100 = 33.33%</t>
-  </si>
-  <si>
     <t>Test Execution</t>
   </si>
   <si>
     <t>(Executed ÷ Total) × 100</t>
   </si>
   <si>
-    <t>(12 ÷ 12) × 100 = 100%</t>
-  </si>
-  <si>
     <t>Test Coverage</t>
   </si>
   <si>
@@ -251,32 +191,204 @@
     <t xml:space="preserve">MYNTRA </t>
   </si>
   <si>
-    <t>Search results should primarily display plain blue dresses matching the search criteria</t>
-  </si>
-  <si>
-    <t>Search results displayed dresses with combined/multiple colours</t>
-  </si>
-  <si>
-    <t>Search for “Plain Blue Dress”</t>
-  </si>
-  <si>
-    <t>Verify OTP field accepts only numeric input</t>
-  </si>
-  <si>
-    <t>Field should reject non-numeric characters</t>
-  </si>
-  <si>
-    <t>Alphabets were accepted in the OTP input field</t>
-  </si>
-  <si>
     <t xml:space="preserve"> '</t>
+  </si>
+  <si>
+    <t>Login with valid credentials</t>
+  </si>
+  <si>
+    <t>User should log in successfully</t>
+  </si>
+  <si>
+    <t>Login with invalid credentials</t>
+  </si>
+  <si>
+    <t>Error/verification message should be displayed</t>
+  </si>
+  <si>
+    <t>Search for an existing product</t>
+  </si>
+  <si>
+    <t>Relevant products should be displayed</t>
+  </si>
+  <si>
+    <t>Relevant products displayed</t>
+  </si>
+  <si>
+    <t>Results should match plain blue dresses</t>
+  </si>
+  <si>
+    <t>Combined-colour dresses are displayed</t>
+  </si>
+  <si>
+    <t>Search for a non-existing product</t>
+  </si>
+  <si>
+    <t>No matching products should be displayed</t>
+  </si>
+  <si>
+    <t>No matching products displayed</t>
+  </si>
+  <si>
+    <t>Apply Blue colour filter</t>
+  </si>
+  <si>
+    <t>Blue products should be displayed</t>
+  </si>
+  <si>
+    <t>Blue products displayed</t>
+  </si>
+  <si>
+    <t>Apply Size M filter</t>
+  </si>
+  <si>
+    <t>Products available in Size M should be displayed</t>
+  </si>
+  <si>
+    <t>Size M products displayed</t>
+  </si>
+  <si>
+    <t>Apply price filter ₹500–₹1,000</t>
+  </si>
+  <si>
+    <t>Products should be within the selected range</t>
+  </si>
+  <si>
+    <t>Products displayed within the range</t>
+  </si>
+  <si>
+    <t>Sort products by Price: Low to High</t>
+  </si>
+  <si>
+    <t>Products should be arranged from low to high price</t>
+  </si>
+  <si>
+    <t>Products sorted correctly</t>
+  </si>
+  <si>
+    <t>Open a product</t>
+  </si>
+  <si>
+    <t>Select an available size</t>
+  </si>
+  <si>
+    <t>Select an unavailable size</t>
+  </si>
+  <si>
+    <t>TC13</t>
+  </si>
+  <si>
+    <t>Add product to Bag</t>
+  </si>
+  <si>
+    <t>TC14</t>
+  </si>
+  <si>
+    <t>Remove product from Bag</t>
+  </si>
+  <si>
+    <t>Product should be removed</t>
+  </si>
+  <si>
+    <t>Product removed successfully</t>
+  </si>
+  <si>
+    <t>TC15</t>
+  </si>
+  <si>
+    <t>Change product quantity</t>
+  </si>
+  <si>
+    <t>Selected quantity should be updated</t>
+  </si>
+  <si>
+    <t>Quantity updated successfully</t>
+  </si>
+  <si>
+    <t>TC16</t>
+  </si>
+  <si>
+    <t>Enter invalid delivery pincode</t>
+  </si>
+  <si>
+    <t>Invalid pincode message should be displayed</t>
+  </si>
+  <si>
+    <t>“Invalid Pincode” displayed</t>
+  </si>
+  <si>
+    <t>TC17</t>
+  </si>
+  <si>
+    <t>Enter valid delivery pincode</t>
+  </si>
+  <si>
+    <t>Delivery availability should be displayed</t>
+  </si>
+  <si>
+    <t>Delivery availability displayed</t>
+  </si>
+  <si>
+    <t>TC18</t>
+  </si>
+  <si>
+    <t>Apply invalid/expired coupon</t>
+  </si>
+  <si>
+    <t>Coupon should not be applied</t>
+  </si>
+  <si>
+    <t>Coupon rejected</t>
+  </si>
+  <si>
+    <t>TC19</t>
+  </si>
+  <si>
+    <t>Make payment using valid payment details</t>
+  </si>
+  <si>
+    <t>Payment should be successful</t>
+  </si>
+  <si>
+    <t>Payment successful</t>
+  </si>
+  <si>
+    <t>TC20</t>
+  </si>
+  <si>
+    <t>Place order with valid details</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Search for </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“Plain Blue Dress”</t>
+    </r>
+  </si>
+  <si>
+    <t>(19 ÷ 20) × 100 = 95%</t>
+  </si>
+  <si>
+    <t>(1 ÷ 20) × 100 = 5%</t>
+  </si>
+  <si>
+    <t>(20 ÷ 20) × 100 = 100%</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -300,6 +412,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -309,7 +436,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -327,15 +454,6 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -368,42 +486,54 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="medium">
+      <left style="medium">
         <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -412,34 +542,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -774,12 +876,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F4890E2-1CF4-46D6-96F4-60A99F56B2F1}">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="20.77734375" customWidth="1"/>
-    <col min="3" max="3" width="50.77734375" customWidth="1"/>
-    <col min="4" max="6" width="20.77734375" customWidth="1"/>
+    <col min="1" max="5" width="30.77734375" customWidth="1"/>
+    <col min="6" max="6" width="20.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -787,10 +888,10 @@
     </row>
     <row r="2" spans="1:6" ht="23.4" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>70</v>
+        <v>51</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>50</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -800,352 +901,584 @@
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F5" s="2"/>
     </row>
-    <row r="6" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>4</v>
+      </c>
       <c r="F6" s="2"/>
     </row>
-    <row r="7" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>4</v>
+    <row r="7" spans="1:6" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>7</v>
       </c>
       <c r="F7" s="2"/>
     </row>
-    <row r="8" spans="1:6" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="9" t="s">
+    <row r="8" spans="1:6" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="9" t="s">
-        <v>9</v>
+      <c r="B8" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>7</v>
       </c>
       <c r="F8" s="2"/>
     </row>
-    <row r="9" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="9" t="s">
+    <row r="9" spans="1:6" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="1:6" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="2"/>
-    </row>
-    <row r="10" spans="1:6" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>37</v>
+      <c r="B10" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>60</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>9</v>
       </c>
       <c r="F10" s="2"/>
     </row>
-    <row r="11" spans="1:6" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="9" t="s">
+    <row r="11" spans="1:6" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="1:6" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="1:6" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="1:6" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B15" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="B16" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+    </row>
+    <row r="32" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+    </row>
+    <row r="35" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="7"/>
+    </row>
+    <row r="36" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E36" s="2"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="13">
+        <v>1</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D37" s="14">
+        <v>20</v>
+      </c>
+      <c r="E37" s="2"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="13">
+        <v>2</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C38" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D38" s="14">
+        <v>19</v>
+      </c>
+      <c r="E38" s="2"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="13">
+        <v>3</v>
+      </c>
+      <c r="B39" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E11" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="2"/>
-    </row>
-    <row r="12" spans="1:6" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="9" t="s">
+      <c r="C39" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="D39" s="14">
+        <v>1</v>
+      </c>
+      <c r="E39" s="2"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="13">
+        <v>4</v>
+      </c>
+      <c r="B40" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="C40" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E12" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="2"/>
-    </row>
-    <row r="13" spans="1:6" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="9" t="s">
+      <c r="D40" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E40" s="2"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="13">
+        <v>5</v>
+      </c>
+      <c r="B41" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C41" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D41" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="E41" s="2"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="13">
+        <v>6</v>
+      </c>
+      <c r="B42" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="9" t="s">
+      <c r="C42" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D42" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="E42" s="2"/>
+    </row>
+    <row r="43" spans="1:5" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="3">
+        <v>7</v>
+      </c>
+      <c r="B43" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E16" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="22" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="7" t="s">
+      <c r="C43" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="D43" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C22" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="10">
-        <v>1</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="D23" s="13">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="9">
-        <v>2</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="D24" s="13">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="9">
-        <v>3</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="D25" s="13">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="9">
-        <v>4</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="9">
-        <v>5</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="9">
-        <v>6</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="4">
-        <v>7</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>69</v>
-      </c>
+      <c r="E43" s="2"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="2"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" s="2"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" s="2"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" s="2"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
